--- a/data/trans_dic/IP2002-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les han extraído dientes por caries o por otro motivo</t>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,09</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,09</t>
+          <t>0,53; 3,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,93</t>
+          <t>1,12; 4,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,83</t>
+          <t>0,96; 4,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,33</t>
+          <t>1,58; 6,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,31</t>
+          <t>0,79; 3,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,83</t>
+          <t>2,41; 6,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,32</t>
+          <t>0,21; 2,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,9</t>
+          <t>1,8; 7,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,63</t>
+          <t>0,81; 2,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,1</t>
+          <t>2,21; 5,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,66</t>
+          <t>0,72; 2,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,71</t>
+          <t>2,17; 6,01</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 16,15</t>
+          <t>7,49; 16,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 13,21</t>
+          <t>5,45; 12,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 14,15</t>
+          <t>7,4; 14,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,37</t>
+          <t>6,1; 14,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 19,87</t>
+          <t>10,65; 20,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,79</t>
+          <t>7,21; 15,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 11,11</t>
+          <t>4,44; 10,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,78</t>
+          <t>2,8; 8,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 16,6</t>
+          <t>10,32; 17,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 12,92</t>
+          <t>7,27; 12,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,37</t>
+          <t>6,6; 11,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 9,3</t>
+          <t>4,97; 9,38</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 18,11</t>
+          <t>10,5; 18,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 14,26</t>
+          <t>6,66; 14,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 13,58</t>
+          <t>6,09; 14,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,56</t>
+          <t>3,89; 9,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 16,72</t>
+          <t>8,97; 16,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 15,36</t>
+          <t>7,88; 15,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 14,81</t>
+          <t>6,95; 15,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,33</t>
+          <t>4,15; 9,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,07</t>
+          <t>10,23; 15,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 13,53</t>
+          <t>8,22; 13,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 13,04</t>
+          <t>7,4; 13,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,55</t>
+          <t>4,57; 8,87</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,91</t>
+          <t>5,52; 8,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,99</t>
+          <t>4,13; 7,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,84</t>
+          <t>4,77; 7,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,6</t>
+          <t>4,46; 7,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,2</t>
+          <t>5,89; 9,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,66</t>
+          <t>5,41; 8,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,27</t>
+          <t>3,73; 6,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,7</t>
+          <t>3,73; 6,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,36</t>
+          <t>6,05; 8,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,39</t>
+          <t>5,23; 7,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,56</t>
+          <t>4,54; 6,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,73</t>
+          <t>4,43; 6,64</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3516</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3520</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3593</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5896</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4740</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5334</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11318</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6889</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7695</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17214</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6830</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12223</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1343; 8049</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2635; 10969</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2010; 9191</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2517; 9793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2007; 8234</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6472; 18091</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>552; 5648</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3273; 12730</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4103; 13203</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>11176; 25516</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3344; 12187</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7390; 20479</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15163</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13700</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19757</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15979</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20494</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17326</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13484</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10546</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>35656</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>31026</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>33242</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>26525</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9558; 21624</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8558; 20323</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13984; 27574</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10555; 24727</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>15066; 28914</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11384; 25169</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8380; 20123</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5952; 17377</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>27771; 45730</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22905; 39919</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>24923; 42586</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>19143; 36161</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>27065</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17076</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16436</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17536</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25283</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20039</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18142</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>19375</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>52348</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37115</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>34578</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>36911</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>20376; 35822</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11369; 25243</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10527; 24438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10708; 27093</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>18419; 33050</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14173; 28443</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>12095; 26454</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>12667; 29062</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>40863; 62632</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>28814; 47963</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>25658; 45383</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>26540; 51551</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>45821</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36672</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40933</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38849</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>37518</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>95700</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>85356</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>74649</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>76367</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>35622; 57038</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27367; 47763</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31401; 52486</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29229; 51005</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>40380; 61774</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>38044; 60920</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26153; 45040</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>27882; 50173</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>80403; 111998</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>71459; 101364</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>61774; 90001</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>62221; 93246</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2002-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Edad-trans_dic.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 7,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,19</t>
+          <t>0,53; 3,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,64</t>
+          <t>1,24; 4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,39</t>
+          <t>0,98; 4,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,15</t>
+          <t>1,64; 6,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,25</t>
+          <t>0,55; 3,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,73</t>
+          <t>2,33; 6,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,19</t>
+          <t>0,21; 2,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 7,01</t>
+          <t>1,71; 7,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,61</t>
+          <t>0,83; 2,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,05</t>
+          <t>2,12; 5,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,61</t>
+          <t>0,72; 2,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,01</t>
+          <t>2,12; 5,62</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 16,95</t>
+          <t>7,78; 16,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 12,94</t>
+          <t>5,37; 13,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,6</t>
+          <t>7,39; 14,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 14,29</t>
+          <t>5,77; 13,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,65; 20,43</t>
+          <t>10,22; 20,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,95</t>
+          <t>7,67; 16,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,67</t>
+          <t>4,62; 11,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,18</t>
+          <t>2,73; 8,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 17,0</t>
+          <t>9,94; 16,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 12,68</t>
+          <t>7,38; 12,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 11,28</t>
+          <t>6,56; 11,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,38</t>
+          <t>4,98; 9,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,5; 18,46</t>
+          <t>10,41; 18,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 14,79</t>
+          <t>6,47; 13,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 14,15</t>
+          <t>6,23; 13,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,84</t>
+          <t>3,73; 9,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 16,09</t>
+          <t>9,01; 16,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 15,81</t>
+          <t>7,8; 15,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 15,2</t>
+          <t>7,02; 15,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,51</t>
+          <t>3,95; 9,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 15,68</t>
+          <t>10,38; 15,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,68</t>
+          <t>8,05; 13,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 13,09</t>
+          <t>7,48; 12,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,87</t>
+          <t>4,61; 8,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,84</t>
+          <t>5,64; 9,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,21</t>
+          <t>4,28; 7,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,97</t>
+          <t>4,73; 7,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,77</t>
+          <t>4,34; 7,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,02</t>
+          <t>5,87; 9,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,67</t>
+          <t>5,48; 8,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,43</t>
+          <t>3,61; 6,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,71</t>
+          <t>3,66; 6,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,42</t>
+          <t>6,12; 8,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,42</t>
+          <t>5,26; 7,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,62</t>
+          <t>4,51; 6,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,64</t>
+          <t>4,39; 6,6</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3516</t>
+          <t>0; 3538</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3557</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1343; 8049</t>
+          <t>1329; 7826</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2635; 10969</t>
+          <t>2919; 11111</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2010; 9191</t>
+          <t>2048; 10164</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2517; 9793</t>
+          <t>2605; 9976</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2007; 8234</t>
+          <t>1397; 8274</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6472; 18091</t>
+          <t>6278; 18202</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>552; 5648</t>
+          <t>550; 5493</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3273; 12730</t>
+          <t>3111; 13702</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4103; 13203</t>
+          <t>4189; 13476</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11176; 25516</t>
+          <t>10714; 25455</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3344; 12187</t>
+          <t>3363; 12552</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7390; 20479</t>
+          <t>7230; 19134</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9558; 21624</t>
+          <t>9922; 21654</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8558; 20323</t>
+          <t>8433; 20952</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13984; 27574</t>
+          <t>13968; 27923</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10555; 24727</t>
+          <t>9990; 23088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15066; 28914</t>
+          <t>14460; 28470</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11384; 25169</t>
+          <t>12098; 25925</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8380; 20123</t>
+          <t>8708; 20738</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5952; 17377</t>
+          <t>5809; 17014</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27771; 45730</t>
+          <t>26737; 44705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22905; 39919</t>
+          <t>23241; 39465</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24923; 42586</t>
+          <t>24747; 42765</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19143; 36161</t>
+          <t>19216; 36530</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20376; 35822</t>
+          <t>20205; 35987</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11369; 25243</t>
+          <t>11055; 23502</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10527; 24438</t>
+          <t>10765; 22759</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10708; 27093</t>
+          <t>10269; 26941</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18419; 33050</t>
+          <t>18511; 33466</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14173; 28443</t>
+          <t>14032; 28158</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12095; 26454</t>
+          <t>12219; 26268</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12667; 29062</t>
+          <t>12072; 28716</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40863; 62632</t>
+          <t>41463; 63740</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28814; 47963</t>
+          <t>28246; 47007</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25658; 45383</t>
+          <t>25924; 44555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26540; 51551</t>
+          <t>26778; 51424</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35622; 57038</t>
+          <t>36410; 58466</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27367; 47763</t>
+          <t>28359; 47592</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31401; 52486</t>
+          <t>31165; 52117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29229; 51005</t>
+          <t>28474; 50197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40380; 61774</t>
+          <t>40242; 62884</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38044; 60920</t>
+          <t>38542; 60200</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26153; 45040</t>
+          <t>25286; 44593</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27882; 50173</t>
+          <t>27386; 49894</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80403; 111998</t>
+          <t>81343; 110831</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71459; 101364</t>
+          <t>71872; 103048</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61774; 90001</t>
+          <t>61321; 89220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>62221; 93246</t>
+          <t>61602; 92702</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2002-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,29 +664,29 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -732,29 +732,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,74</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,38</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,1</t>
+          <t>0,54; 3,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,7</t>
+          <t>2,31; 6,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,86</t>
+          <t>0,21; 2,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,27</t>
+          <t>1,84; 7,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,27</t>
+          <t>0,53; 3,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,77</t>
+          <t>1,21; 4,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,13</t>
+          <t>0,98; 4,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,55</t>
+          <t>1,62; 7,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,66</t>
+          <t>0,81; 2,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,04</t>
+          <t>2,15; 5,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,69</t>
+          <t>0,76; 2,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,62</t>
+          <t>2,23; 6,18</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,48%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11,89%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,72%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,46%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 16,98</t>
+          <t>10,0; 19,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 13,34</t>
+          <t>7,33; 15,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 14,78</t>
+          <t>4,48; 11,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 13,34</t>
+          <t>2,6; 8,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,12</t>
+          <t>7,19; 16,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 16,43</t>
+          <t>5,54; 13,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 11,0</t>
+          <t>7,09; 14,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,01</t>
+          <t>5,86; 13,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 16,62</t>
+          <t>10,26; 16,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 12,53</t>
+          <t>7,3; 12,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,33</t>
+          <t>6,49; 11,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,47</t>
+          <t>4,84; 9,31</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,94%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>6,34%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 18,54</t>
+          <t>9,29; 16,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 13,77</t>
+          <t>7,79; 15,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 13,17</t>
+          <t>6,92; 14,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,78</t>
+          <t>3,86; 9,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 16,3</t>
+          <t>10,37; 18,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 15,65</t>
+          <t>6,69; 14,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 15,09</t>
+          <t>6,25; 13,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 9,4</t>
+          <t>4,13; 9,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 15,96</t>
+          <t>10,49; 16,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 13,4</t>
+          <t>8,02; 13,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 12,85</t>
+          <t>7,41; 13,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,85</t>
+          <t>4,62; 8,48</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,1%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,06</t>
+          <t>5,91; 9,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,18</t>
+          <t>5,35; 8,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,91</t>
+          <t>3,63; 6,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,65</t>
+          <t>3,6; 6,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,18</t>
+          <t>5,56; 8,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,57</t>
+          <t>4,12; 6,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,36</t>
+          <t>4,76; 7,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,68</t>
+          <t>4,59; 7,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,33</t>
+          <t>6,16; 8,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,55</t>
+          <t>5,23; 7,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,56</t>
+          <t>4,55; 6,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,6</t>
+          <t>4,56; 6,81</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1592,29 +1592,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>565</t>
         </is>
       </c>
     </row>
@@ -1660,29 +1660,29 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 3070</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3538</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3557</t>
+          <t>0; 2850</t>
         </is>
       </c>
     </row>
@@ -1717,37 +1717,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11318</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6056</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3593</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5896</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4740</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5334</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4102</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11318</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>11361</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1329; 7826</t>
+          <t>1378; 8388</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2919; 11111</t>
+          <t>6211; 18378</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2048; 10164</t>
+          <t>545; 5982</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2605; 9976</t>
+          <t>2886; 11325</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1397; 8274</t>
+          <t>1327; 7809</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6278; 18202</t>
+          <t>2867; 11639</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>550; 5493</t>
+          <t>2060; 10105</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3111; 13702</t>
+          <t>2349; 10231</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4189; 13476</t>
+          <t>4118; 13322</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10714; 25455</t>
+          <t>10851; 25747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3363; 12552</t>
+          <t>3551; 12440</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7230; 19134</t>
+          <t>6739; 18662</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20494</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17326</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13484</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9575</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>15163</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>13700</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>19757</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15979</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20494</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17326</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13484</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26525</t>
+          <t>25817</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9922; 21654</t>
+          <t>14148; 28120</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8433; 20952</t>
+          <t>11573; 24921</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13968; 27923</t>
+          <t>8454; 20956</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9990; 23088</t>
+          <t>5208; 16873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14460; 28470</t>
+          <t>9176; 20604</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12098; 25925</t>
+          <t>8708; 20744</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8708; 20738</t>
+          <t>13396; 26732</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5809; 17014</t>
+          <t>10231; 23290</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26737; 44705</t>
+          <t>27596; 44657</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23241; 39465</t>
+          <t>22986; 40678</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24747; 42765</t>
+          <t>24494; 42910</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19216; 36530</t>
+          <t>18123; 34891</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25283</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20039</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18142</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18098</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>27065</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>17076</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>16436</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17536</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25283</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20039</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18142</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>34832</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20205; 35987</t>
+          <t>19077; 34336</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11055; 23502</t>
+          <t>14011; 27642</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10765; 22759</t>
+          <t>12049; 25776</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10269; 26941</t>
+          <t>11302; 26453</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18511; 33466</t>
+          <t>20133; 35153</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14032; 28158</t>
+          <t>11416; 24350</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12219; 26268</t>
+          <t>10791; 23462</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12072; 28716</t>
+          <t>10584; 24306</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41463; 63740</t>
+          <t>41888; 64208</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28246; 47007</t>
+          <t>28119; 47460</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25924; 44555</t>
+          <t>25710; 45212</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26778; 51424</t>
+          <t>25392; 46583</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34294</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>45821</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>36672</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>40933</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>38849</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>49879</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>48684</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>33716</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76367</t>
+          <t>72575</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36410; 58466</t>
+          <t>40464; 63034</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28359; 47592</t>
+          <t>37611; 60864</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31165; 52117</t>
+          <t>25408; 43923</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28474; 50197</t>
+          <t>24835; 46040</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40242; 62884</t>
+          <t>35874; 57442</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38542; 60200</t>
+          <t>27318; 46356</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25286; 44593</t>
+          <t>31333; 51664</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27386; 49894</t>
+          <t>28520; 49187</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81343; 110831</t>
+          <t>81953; 111232</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71872; 103048</t>
+          <t>71434; 100916</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61321; 89220</t>
+          <t>61818; 89187</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61602; 92702</t>
+          <t>59739; 89200</t>
         </is>
       </c>
     </row>
